--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-administration-produit-de-sante.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-administration-produit-de-sante.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$133</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4158" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4190" uniqueCount="400">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -661,6 +661,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>SubstanceAdministration.statusCode</t>
@@ -1175,6 +1179,22 @@
   </si>
   <si>
     <t>Material.lotNumberText</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.manufacturedProduct.manufacturedMaterial.sdtcExpirationTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS
+</t>
+  </si>
+  <si>
+    <t>The date and time the manufacturer no longer ensures the safety, quality, and/or proper functioning of the material.</t>
+  </si>
+  <si>
+    <t>There is a need in many situations that the materials used are of a specific quality or potency or functional status. The ending date for this guarantee is specified by the manufacturer. After that date, while the material may still provide the same characteristics, the manufacturer no longer takes responsibility that the product will perform as specified and denies responsibility for failure of the material after that date.</t>
+  </si>
+  <si>
+    <t>Material.sdtcExpirationTime</t>
   </si>
   <si>
     <t>SubstanceAdministration.consumable.manufacturedProduct.manufacturerOrganization</t>
@@ -1571,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK132"/>
+  <dimension ref="A1:AK133"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="100.08203125" customWidth="true" bestFit="true"/>
@@ -1588,7 +1608,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -5589,7 +5609,7 @@
         <v>74</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>74</v>
+        <v>209</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>74</v>
@@ -5597,10 +5617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5626,10 +5646,10 @@
         <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5660,7 +5680,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>74</v>
@@ -5678,7 +5698,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5698,10 +5718,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5799,10 +5819,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5831,7 +5851,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5843,7 +5863,7 @@
         <v>74</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>74</v>
@@ -5882,7 +5902,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5902,17 +5922,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5934,7 +5954,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5985,7 +6005,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6005,17 +6025,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -6037,7 +6057,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6088,7 +6108,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6108,17 +6128,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -6140,7 +6160,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6191,7 +6211,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6211,17 +6231,17 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
@@ -6243,7 +6263,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6294,7 +6314,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6314,10 +6334,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6340,11 +6360,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6395,7 +6415,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6415,10 +6435,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6445,7 +6465,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6496,7 +6516,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6516,17 +6536,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6548,7 +6568,7 @@
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6599,7 +6619,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6619,17 +6639,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6647,11 +6667,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6702,7 +6722,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6722,17 +6742,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6754,7 +6774,7 @@
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6805,7 +6825,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6825,10 +6845,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6851,7 +6871,7 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6904,7 +6924,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6924,10 +6944,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6950,7 +6970,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6983,7 +7003,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -7001,7 +7021,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7021,10 +7041,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7047,7 +7067,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -7100,7 +7120,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7120,10 +7140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7146,13 +7166,13 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7183,7 +7203,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7201,7 +7221,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7221,10 +7241,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7280,25 +7300,25 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7318,10 +7338,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7344,13 +7364,13 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7401,7 +7421,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7421,10 +7441,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7447,13 +7467,13 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7504,7 +7524,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7524,10 +7544,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7550,7 +7570,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7603,7 +7623,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7623,10 +7643,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7649,7 +7669,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7682,25 +7702,25 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7720,10 +7740,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7746,13 +7766,13 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7803,7 +7823,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -7823,10 +7843,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7924,10 +7944,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8025,10 +8045,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8126,10 +8146,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8227,10 +8247,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8330,10 +8350,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8433,10 +8453,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8536,10 +8556,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8639,10 +8659,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8740,10 +8760,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8777,7 +8797,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>74</v>
@@ -8799,7 +8819,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>74</v>
@@ -8817,7 +8837,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8837,10 +8857,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8863,13 +8883,13 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8920,7 +8940,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -8940,10 +8960,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9041,10 +9061,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9142,10 +9162,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9243,10 +9263,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9344,10 +9364,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9447,10 +9467,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9550,10 +9570,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9653,10 +9673,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9756,10 +9776,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9857,10 +9877,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9894,7 +9914,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>74</v>
@@ -9916,7 +9936,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>74</v>
@@ -9934,7 +9954,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9954,10 +9974,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10033,7 +10053,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10053,10 +10073,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10079,7 +10099,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10132,7 +10152,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10152,10 +10172,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10178,7 +10198,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10231,7 +10251,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10251,10 +10271,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10277,7 +10297,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10330,7 +10350,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10350,10 +10370,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10451,10 +10471,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10552,10 +10572,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10653,10 +10673,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10754,10 +10774,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10857,10 +10877,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10960,10 +10980,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11063,10 +11083,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11166,10 +11186,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11267,10 +11287,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11304,7 +11324,7 @@
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>74</v>
@@ -11326,7 +11346,7 @@
       </c>
       <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>74</v>
@@ -11344,7 +11364,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11364,10 +11384,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11401,7 +11421,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>74</v>
@@ -11423,7 +11443,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>74</v>
@@ -11441,7 +11461,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11461,10 +11481,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11487,13 +11507,13 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11524,7 +11544,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>74</v>
@@ -11542,7 +11562,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11562,10 +11582,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11663,10 +11683,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11695,7 +11715,7 @@
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11746,7 +11766,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11766,17 +11786,17 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>80</v>
@@ -11798,7 +11818,7 @@
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11849,7 +11869,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11869,17 +11889,17 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F102" t="s" s="2">
         <v>80</v>
@@ -11901,7 +11921,7 @@
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11952,7 +11972,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11972,17 +11992,17 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F103" t="s" s="2">
         <v>80</v>
@@ -12004,7 +12024,7 @@
       </c>
       <c r="L103" s="2"/>
       <c r="M103" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12055,7 +12075,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12075,17 +12095,17 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>80</v>
@@ -12107,7 +12127,7 @@
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12158,7 +12178,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12178,10 +12198,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12204,11 +12224,11 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12259,7 +12279,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12279,10 +12299,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12309,7 +12329,7 @@
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12360,7 +12380,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12380,17 +12400,17 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F107" t="s" s="2">
         <v>75</v>
@@ -12412,7 +12432,7 @@
       </c>
       <c r="L107" s="2"/>
       <c r="M107" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12463,7 +12483,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12483,10 +12503,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12584,10 +12604,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12685,10 +12705,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12788,10 +12808,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12889,10 +12909,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12992,10 +13012,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13093,10 +13113,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13190,10 +13210,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13295,10 +13315,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13398,10 +13418,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13493,7 +13513,7 @@
         <v>74</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>74</v>
+        <v>209</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>74</v>
@@ -13501,17 +13521,17 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F118" t="s" s="2">
         <v>80</v>
@@ -13529,11 +13549,11 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -13584,7 +13604,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13604,17 +13624,17 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F119" t="s" s="2">
         <v>80</v>
@@ -13635,10 +13655,10 @@
         <v>160</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -13689,7 +13709,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13709,10 +13729,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13735,13 +13755,13 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -13792,7 +13812,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -13812,10 +13832,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13838,13 +13858,13 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13895,7 +13915,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -13915,10 +13935,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13941,12 +13961,16 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L122" s="2"/>
-      <c r="M122" s="2"/>
+      <c r="M122" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
+      <c r="O122" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>74</v>
       </c>
@@ -13994,7 +14018,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14014,10 +14038,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14040,7 +14064,7 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -14093,7 +14117,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14113,10 +14137,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14127,7 +14151,7 @@
         <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>74</v>
@@ -14139,7 +14163,7 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -14192,13 +14216,13 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>74</v>
@@ -14212,10 +14236,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14238,7 +14262,7 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14291,7 +14315,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14311,10 +14335,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14337,7 +14361,7 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14390,7 +14414,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14410,10 +14434,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14436,7 +14460,7 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14489,7 +14513,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14509,10 +14533,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14535,7 +14559,7 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -14588,7 +14612,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14608,10 +14632,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14634,7 +14658,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14687,7 +14711,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14707,10 +14731,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14733,7 +14757,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -14786,7 +14810,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14806,10 +14830,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14832,7 +14856,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -14885,7 +14909,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -14905,10 +14929,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -14931,7 +14955,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -14984,7 +15008,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15002,8 +15026,107 @@
         <v>74</v>
       </c>
     </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L133" s="2"/>
+      <c r="M133" s="2"/>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK132">
+  <autoFilter ref="A1:AK133">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15013,7 +15136,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI131">
+  <conditionalFormatting sqref="A2:AI132">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
